--- a/naver-place-crawler/results_hair/수영구_미용실.xlsx
+++ b/naver-place-crawler/results_hair/수영구_미용실.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V259"/>
+  <dimension ref="A1:V332"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -22329,39 +22329,35 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>두피,탈모관리</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>나와모랩 부산수영구1호점</t>
-        </is>
-      </c>
-      <c r="C239" t="inlineStr">
-        <is>
-          <t>nawamolab@naver.com</t>
-        </is>
-      </c>
+          <t>유스헤어샾</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr"/>
       <c r="D239" t="inlineStr"/>
       <c r="E239" t="inlineStr">
         <is>
-          <t>0507-1377-7665</t>
+          <t>0507-1383-2542</t>
         </is>
       </c>
       <c r="F239" t="inlineStr"/>
       <c r="G239" t="inlineStr">
         <is>
-          <t>부산광역시 수영구 수영로741번길 12 105호</t>
+          <t>부산광역시 수영구 남천동로 91 301동 1층 106-3호</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>https://litt.ly/nawamolab</t>
+          <t>https://www.instagram.com/youth_khj/</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J239" t="inlineStr">
@@ -22387,17 +22383,17 @@
       </c>
       <c r="O239" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P239" t="n">
-        <v>0</v>
+        <v>576</v>
       </c>
       <c r="Q239" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="R239" t="n">
-        <v>0</v>
+        <v>607</v>
       </c>
       <c r="S239" t="inlineStr">
         <is>
@@ -22406,12 +22402,12 @@
       </c>
       <c r="T239" t="inlineStr">
         <is>
-          <t>2020236542</t>
+          <t>1132104515</t>
         </is>
       </c>
       <c r="U239" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2020236542</t>
+          <t>https://m.place.naver.com/place/1132104515</t>
         </is>
       </c>
       <c r="V239" t="inlineStr">
@@ -22423,30 +22419,30 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>미용</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>해변살롱</t>
+          <t>숙이네미장원</t>
         </is>
       </c>
       <c r="C240" t="inlineStr"/>
       <c r="D240" t="inlineStr"/>
       <c r="E240" t="inlineStr">
         <is>
-          <t>051-913-1578</t>
+          <t>0507-1449-0639</t>
         </is>
       </c>
       <c r="F240" t="inlineStr"/>
       <c r="G240" t="inlineStr">
         <is>
-          <t>부산광역시 수영구 수영로388번길 46 2층</t>
+          <t>부산광역시 수영구 연수로269번길 22 1층</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/_marrie_157</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I240" t="inlineStr">
@@ -22456,7 +22452,7 @@
       </c>
       <c r="J240" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K240" t="inlineStr">
@@ -22477,17 +22473,17 @@
       </c>
       <c r="O240" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P240" t="n">
-        <v>88</v>
+        <v>2</v>
       </c>
       <c r="Q240" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R240" t="n">
-        <v>89</v>
+        <v>2</v>
       </c>
       <c r="S240" t="inlineStr">
         <is>
@@ -22496,12 +22492,12 @@
       </c>
       <c r="T240" t="inlineStr">
         <is>
-          <t>1855340486</t>
+          <t>1390090106</t>
         </is>
       </c>
       <c r="U240" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1855340486</t>
+          <t>https://m.place.naver.com/place/1390090106</t>
         </is>
       </c>
       <c r="V240" t="inlineStr">
@@ -22513,25 +22509,25 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>미용</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>샵132</t>
+          <t>윤새벽의새벽헤어</t>
         </is>
       </c>
       <c r="C241" t="inlineStr"/>
       <c r="D241" t="inlineStr"/>
       <c r="E241" t="inlineStr">
         <is>
-          <t>070-3333-3535</t>
+          <t>051-852-6357</t>
         </is>
       </c>
       <c r="F241" t="inlineStr"/>
       <c r="G241" t="inlineStr">
         <is>
-          <t>부산광역시 수영구 황령대로473번길 15 1층 132호</t>
+          <t>부산광역시 수영구 연수로401번길 3</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
@@ -22571,13 +22567,13 @@
         </is>
       </c>
       <c r="P241" t="n">
-        <v>3</v>
+        <v>44</v>
       </c>
       <c r="Q241" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R241" t="n">
-        <v>3</v>
+        <v>45</v>
       </c>
       <c r="S241" t="inlineStr">
         <is>
@@ -22586,12 +22582,12 @@
       </c>
       <c r="T241" t="inlineStr">
         <is>
-          <t>1803491672</t>
+          <t>1570401947</t>
         </is>
       </c>
       <c r="U241" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1803491672</t>
+          <t>https://m.place.naver.com/place/1570401947</t>
         </is>
       </c>
       <c r="V241" t="inlineStr">
@@ -22603,45 +22599,49 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>반려동물미용</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>민츄츄</t>
-        </is>
-      </c>
-      <c r="C242" t="inlineStr"/>
+          <t>헤어스토리</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>jbjoo0537@naver.com</t>
+        </is>
+      </c>
       <c r="D242" t="inlineStr"/>
       <c r="E242" t="inlineStr">
         <is>
-          <t>0507-1327-2177</t>
+          <t>051-754-8765</t>
         </is>
       </c>
       <c r="F242" t="inlineStr"/>
       <c r="G242" t="inlineStr">
         <is>
-          <t>부산광역시 수영구 민락본동로11번길 21 민츄츄 애견미용실</t>
+          <t>부산광역시 수영구 수미로50번길 5</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I242" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="J242" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K242" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L242" t="inlineStr">
@@ -22657,17 +22657,17 @@
       </c>
       <c r="O242" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P242" t="n">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="Q242" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="R242" t="n">
-        <v>132</v>
+        <v>66</v>
       </c>
       <c r="S242" t="inlineStr">
         <is>
@@ -22676,12 +22676,12 @@
       </c>
       <c r="T242" t="inlineStr">
         <is>
-          <t>1318955783</t>
+          <t>17056916</t>
         </is>
       </c>
       <c r="U242" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1318955783</t>
+          <t>https://m.place.naver.com/place/17056916</t>
         </is>
       </c>
       <c r="V242" t="inlineStr">
@@ -22693,30 +22693,34 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>반려동물미용</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>몽실몽실</t>
-        </is>
-      </c>
-      <c r="C243" t="inlineStr"/>
+          <t>벨헤어</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>rhkdals5566@naver.com</t>
+        </is>
+      </c>
       <c r="D243" t="inlineStr"/>
       <c r="E243" t="inlineStr">
         <is>
-          <t>0507-1358-0740</t>
+          <t>0507-1429-2831</t>
         </is>
       </c>
       <c r="F243" t="inlineStr"/>
       <c r="G243" t="inlineStr">
         <is>
-          <t>부산광역시 수영구 연수로275번길 34 배산정 1층 102호</t>
+          <t>부산광역시 수영구 남천바다로22번길 25 1층</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>http://www.instagram.com/mong.sil123</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I243" t="inlineStr">
@@ -22726,7 +22730,7 @@
       </c>
       <c r="J243" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K243" t="inlineStr">
@@ -22747,17 +22751,17 @@
       </c>
       <c r="O243" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P243" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="Q243" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R243" t="n">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="S243" t="inlineStr">
         <is>
@@ -22766,12 +22770,12 @@
       </c>
       <c r="T243" t="inlineStr">
         <is>
-          <t>1077781280</t>
+          <t>1467101991</t>
         </is>
       </c>
       <c r="U243" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1077781280</t>
+          <t>https://m.place.naver.com/place/1467101991</t>
         </is>
       </c>
       <c r="V243" t="inlineStr">
@@ -22783,30 +22787,34 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>반려동물미용</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>아띠아몽</t>
-        </is>
-      </c>
-      <c r="C244" t="inlineStr"/>
+          <t>나다움헤어</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>nadaumhair@naver.com</t>
+        </is>
+      </c>
       <c r="D244" t="inlineStr"/>
       <c r="E244" t="inlineStr">
         <is>
-          <t>0507-1362-9183</t>
+          <t>0507-1398-2076</t>
         </is>
       </c>
       <c r="F244" t="inlineStr"/>
       <c r="G244" t="inlineStr">
         <is>
-          <t>부산광역시 수영구 남천바다로10번길 16 1층 102호</t>
+          <t>부산광역시 수영구 수영로 776 더샵 센텀포레상가 203호</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/ndu_2022</t>
         </is>
       </c>
       <c r="I244" t="inlineStr">
@@ -22816,7 +22824,7 @@
       </c>
       <c r="J244" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K244" t="inlineStr">
@@ -22837,17 +22845,17 @@
       </c>
       <c r="O244" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P244" t="n">
-        <v>20</v>
+        <v>241</v>
       </c>
       <c r="Q244" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="R244" t="n">
-        <v>23</v>
+        <v>260</v>
       </c>
       <c r="S244" t="inlineStr">
         <is>
@@ -22856,12 +22864,12 @@
       </c>
       <c r="T244" t="inlineStr">
         <is>
-          <t>1439063115</t>
+          <t>1037517426</t>
         </is>
       </c>
       <c r="U244" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1439063115</t>
+          <t>https://m.place.naver.com/place/1037517426</t>
         </is>
       </c>
       <c r="V244" t="inlineStr">
@@ -22873,34 +22881,30 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>반려동물미용</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>동이몽이</t>
-        </is>
-      </c>
-      <c r="C245" t="inlineStr">
-        <is>
-          <t>congzi3388@naver.com</t>
-        </is>
-      </c>
+          <t>스왕헤어샵</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr"/>
       <c r="D245" t="inlineStr"/>
       <c r="E245" t="inlineStr">
         <is>
-          <t>0507-1496-2520</t>
+          <t>051-755-5630</t>
         </is>
       </c>
       <c r="F245" t="inlineStr"/>
       <c r="G245" t="inlineStr">
         <is>
-          <t>부산광역시 수영구 광서로 29 1층</t>
+          <t>부산광역시 수영구 수미로50번길 16</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/dong2mong2_?igsh=azNzbjk2MHIyajc5&amp;utm_source=qr</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I245" t="inlineStr">
@@ -22910,7 +22914,7 @@
       </c>
       <c r="J245" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K245" t="inlineStr">
@@ -22926,22 +22930,22 @@
       <c r="M245" t="inlineStr"/>
       <c r="N245" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="O245" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P245" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="Q245" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="R245" t="n">
-        <v>36</v>
+        <v>2</v>
       </c>
       <c r="S245" t="inlineStr">
         <is>
@@ -22950,12 +22954,12 @@
       </c>
       <c r="T245" t="inlineStr">
         <is>
-          <t>1727573089</t>
+          <t>17058385</t>
         </is>
       </c>
       <c r="U245" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1727573089</t>
+          <t>https://m.place.naver.com/place/17058385</t>
         </is>
       </c>
       <c r="V245" t="inlineStr">
@@ -22967,34 +22971,34 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>반려동물미용</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>댕댕몽띠끄</t>
+          <t>비비엔느헤어 수영광안점</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>dd_mongtique@naver.com</t>
+          <t>vivienne_suyeong@naver.com</t>
         </is>
       </c>
       <c r="D246" t="inlineStr"/>
       <c r="E246" t="inlineStr">
         <is>
-          <t>0507-1366-8269</t>
+          <t>0507-1341-4784</t>
         </is>
       </c>
       <c r="F246" t="inlineStr"/>
       <c r="G246" t="inlineStr">
         <is>
-          <t>부산광역시 수영구 과정로 33-1 1층 1층일부</t>
+          <t>부산광역시 수영구 수영로 710 3층 비비엔느헤어 수영광안점</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/dd_mongtique</t>
+          <t>https://www.instagram.com/vivienne_suyeong</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
@@ -23009,7 +23013,7 @@
       </c>
       <c r="K246" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L246" t="inlineStr">
@@ -23029,13 +23033,13 @@
         </is>
       </c>
       <c r="P246" t="n">
-        <v>14</v>
+        <v>4325</v>
       </c>
       <c r="Q246" t="n">
-        <v>27</v>
+        <v>1844</v>
       </c>
       <c r="R246" t="n">
-        <v>41</v>
+        <v>6169</v>
       </c>
       <c r="S246" t="inlineStr">
         <is>
@@ -23044,12 +23048,12 @@
       </c>
       <c r="T246" t="inlineStr">
         <is>
-          <t>1765807629</t>
+          <t>1736754653</t>
         </is>
       </c>
       <c r="U246" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1765807629</t>
+          <t>https://m.place.naver.com/place/1736754653</t>
         </is>
       </c>
       <c r="V246" t="inlineStr">
@@ -23061,34 +23065,30 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>반려동물미용</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>개팡&amp;스파샤봉</t>
-        </is>
-      </c>
-      <c r="C247" t="inlineStr">
-        <is>
-          <t>mare2674@naver.com</t>
-        </is>
-      </c>
+          <t>노들헤어 앤 메이크업</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr"/>
       <c r="D247" t="inlineStr"/>
       <c r="E247" t="inlineStr">
         <is>
-          <t>0507-1368-5339</t>
+          <t>051-751-3830</t>
         </is>
       </c>
       <c r="F247" t="inlineStr"/>
       <c r="G247" t="inlineStr">
         <is>
-          <t>부산광역시 수영구 광남로 149 대권네오텔 1층 개팡&amp;스파샤봉</t>
+          <t>부산광역시 수영구 광남로 50 1층</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/mare2674</t>
+          <t>https://www.instagram.com/nodeul_ayeon</t>
         </is>
       </c>
       <c r="I247" t="inlineStr">
@@ -23103,7 +23103,7 @@
       </c>
       <c r="K247" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L247" t="inlineStr">
@@ -23123,13 +23123,13 @@
         </is>
       </c>
       <c r="P247" t="n">
-        <v>341</v>
+        <v>1484</v>
       </c>
       <c r="Q247" t="n">
-        <v>298</v>
+        <v>111</v>
       </c>
       <c r="R247" t="n">
-        <v>639</v>
+        <v>1595</v>
       </c>
       <c r="S247" t="inlineStr">
         <is>
@@ -23138,12 +23138,12 @@
       </c>
       <c r="T247" t="inlineStr">
         <is>
-          <t>1439994884</t>
+          <t>1109242043</t>
         </is>
       </c>
       <c r="U247" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1439994884</t>
+          <t>https://m.place.naver.com/place/1109242043</t>
         </is>
       </c>
       <c r="V247" t="inlineStr">
@@ -23155,34 +23155,30 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>이용원</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>코브바버샵</t>
-        </is>
-      </c>
-      <c r="C248" t="inlineStr">
-        <is>
-          <t>kim900_@naver.com</t>
-        </is>
-      </c>
+          <t>나비헤어샵</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr"/>
       <c r="D248" t="inlineStr"/>
       <c r="E248" t="inlineStr">
         <is>
-          <t>0507-1447-7826</t>
+          <t>0507-1306-8559</t>
         </is>
       </c>
       <c r="F248" t="inlineStr"/>
       <c r="G248" t="inlineStr">
         <is>
-          <t>부산광역시 수영구 민락수변로17번길 36 1층 133호</t>
+          <t>부산광역시 수영구 황령대로473번길 16 2층 나비헤어샵</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/cove.barbershop/</t>
+          <t>http://www.instagram.com/gimjagyeong5249</t>
         </is>
       </c>
       <c r="I248" t="inlineStr">
@@ -23217,13 +23213,13 @@
         </is>
       </c>
       <c r="P248" t="n">
-        <v>174</v>
+        <v>124</v>
       </c>
       <c r="Q248" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="R248" t="n">
-        <v>175</v>
+        <v>133</v>
       </c>
       <c r="S248" t="inlineStr">
         <is>
@@ -23232,12 +23228,12 @@
       </c>
       <c r="T248" t="inlineStr">
         <is>
-          <t>2035192863</t>
+          <t>1812798963</t>
         </is>
       </c>
       <c r="U248" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2035192863</t>
+          <t>https://m.place.naver.com/place/1812798963</t>
         </is>
       </c>
       <c r="V248" t="inlineStr">
@@ -23249,25 +23245,25 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>이용원</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>새민락이용원</t>
-        </is>
-      </c>
-      <c r="C249" t="inlineStr">
-        <is>
-          <t>nunnu18@naver.com</t>
-        </is>
-      </c>
+          <t>더자름헤어</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr"/>
       <c r="D249" t="inlineStr"/>
-      <c r="E249" t="inlineStr"/>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>0507-1325-9152</t>
+        </is>
+      </c>
       <c r="F249" t="inlineStr"/>
       <c r="G249" t="inlineStr">
         <is>
-          <t>부산광역시 수영구 광남로258번길 23</t>
+          <t>부산광역시 수영구 남천동로 33 501동 제지16</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
@@ -23307,13 +23303,13 @@
         </is>
       </c>
       <c r="P249" t="n">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="Q249" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R249" t="n">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="S249" t="inlineStr">
         <is>
@@ -23322,12 +23318,12 @@
       </c>
       <c r="T249" t="inlineStr">
         <is>
-          <t>17061619</t>
+          <t>1329990815</t>
         </is>
       </c>
       <c r="U249" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/17061619</t>
+          <t>https://m.place.naver.com/place/1329990815</t>
         </is>
       </c>
       <c r="V249" t="inlineStr">
@@ -23339,34 +23335,30 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>이용원</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>서던브로스바버샵</t>
-        </is>
-      </c>
-      <c r="C250" t="inlineStr">
-        <is>
-          <t>yaganin@naver.com</t>
-        </is>
-      </c>
+          <t>하울케이</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr"/>
       <c r="D250" t="inlineStr"/>
       <c r="E250" t="inlineStr">
         <is>
-          <t>0507-1349-7545</t>
+          <t>0507-1328-5857</t>
         </is>
       </c>
       <c r="F250" t="inlineStr"/>
       <c r="G250" t="inlineStr">
         <is>
-          <t>부산광역시 수영구 광안로16번길 53 1층 101호</t>
+          <t>부산광역시 수영구 과정로41번길 77-3</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/yaganin</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I250" t="inlineStr">
@@ -23376,12 +23368,12 @@
       </c>
       <c r="J250" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K250" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L250" t="inlineStr">
@@ -23397,17 +23389,17 @@
       </c>
       <c r="O250" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P250" t="n">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="Q250" t="n">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="R250" t="n">
-        <v>133</v>
+        <v>34</v>
       </c>
       <c r="S250" t="inlineStr">
         <is>
@@ -23416,12 +23408,12 @@
       </c>
       <c r="T250" t="inlineStr">
         <is>
-          <t>1792037272</t>
+          <t>1220658743</t>
         </is>
       </c>
       <c r="U250" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1792037272</t>
+          <t>https://m.place.naver.com/place/1220658743</t>
         </is>
       </c>
       <c r="V250" t="inlineStr">
@@ -23433,34 +23425,34 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>이용원</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>태창이용원</t>
+          <t>미용실 해랑</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>uldesign17@naver.com</t>
+          <t>tjddnr9218@naver.com</t>
         </is>
       </c>
       <c r="D251" t="inlineStr"/>
       <c r="E251" t="inlineStr">
         <is>
-          <t>051-751-3587</t>
+          <t>0507-1464-5559</t>
         </is>
       </c>
       <c r="F251" t="inlineStr"/>
       <c r="G251" t="inlineStr">
         <is>
-          <t>부산광역시 수영구 구락로 7</t>
+          <t>부산광역시 수영구 수영로 540 1층 미용실 해랑</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/gwangalli_haerang</t>
         </is>
       </c>
       <c r="I251" t="inlineStr">
@@ -23470,7 +23462,7 @@
       </c>
       <c r="J251" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K251" t="inlineStr">
@@ -23491,17 +23483,17 @@
       </c>
       <c r="O251" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P251" t="n">
-        <v>0</v>
+        <v>329</v>
       </c>
       <c r="Q251" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="R251" t="n">
-        <v>0</v>
+        <v>352</v>
       </c>
       <c r="S251" t="inlineStr">
         <is>
@@ -23510,12 +23502,12 @@
       </c>
       <c r="T251" t="inlineStr">
         <is>
-          <t>17058867</t>
+          <t>1148975613</t>
         </is>
       </c>
       <c r="U251" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/17058867</t>
+          <t>https://m.place.naver.com/place/1148975613</t>
         </is>
       </c>
       <c r="V251" t="inlineStr">
@@ -23527,25 +23519,29 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>이용원</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>멋이용원</t>
+          <t>최숙자헤어공간</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>a00031@naver.com</t>
+          <t>gpwjd0849@naver.com</t>
         </is>
       </c>
       <c r="D252" t="inlineStr"/>
-      <c r="E252" t="inlineStr"/>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>051-757-0162</t>
+        </is>
+      </c>
       <c r="F252" t="inlineStr"/>
       <c r="G252" t="inlineStr">
         <is>
-          <t>부산광역시 수영구 망미로8번길 50</t>
+          <t>부산광역시 수영구 연수로282번길 41</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
@@ -23585,13 +23581,13 @@
         </is>
       </c>
       <c r="P252" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q252" t="n">
         <v>0</v>
       </c>
       <c r="R252" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="S252" t="inlineStr">
         <is>
@@ -23600,12 +23596,12 @@
       </c>
       <c r="T252" t="inlineStr">
         <is>
-          <t>1266747351</t>
+          <t>17052035</t>
         </is>
       </c>
       <c r="U252" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1266747351</t>
+          <t>https://m.place.naver.com/place/17052035</t>
         </is>
       </c>
       <c r="V252" t="inlineStr">
@@ -23617,35 +23613,39 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>이용원</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>브런스윅바버샵</t>
-        </is>
-      </c>
-      <c r="C253" t="inlineStr"/>
+          <t>J&amp;W헤어</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>true_true1@naver.com</t>
+        </is>
+      </c>
       <c r="D253" t="inlineStr"/>
       <c r="E253" t="inlineStr">
         <is>
-          <t>0507-1357-8138</t>
+          <t>051-751-1211</t>
         </is>
       </c>
       <c r="F253" t="inlineStr"/>
       <c r="G253" t="inlineStr">
         <is>
-          <t>부산광역시 수영구 광안로35번길 11 1층 브런스윅 바버샵</t>
+          <t>부산광역시 수영구 구락로10번길 23 2층</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/brunswick_barbershop</t>
+          <t>https://blog.naver.com/true_true1</t>
         </is>
       </c>
       <c r="I253" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="J253" t="inlineStr">
@@ -23655,7 +23655,7 @@
       </c>
       <c r="K253" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L253" t="inlineStr">
@@ -23671,17 +23671,17 @@
       </c>
       <c r="O253" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P253" t="n">
-        <v>480</v>
+        <v>22</v>
       </c>
       <c r="Q253" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="R253" t="n">
-        <v>491</v>
+        <v>25</v>
       </c>
       <c r="S253" t="inlineStr">
         <is>
@@ -23690,12 +23690,12 @@
       </c>
       <c r="T253" t="inlineStr">
         <is>
-          <t>1965591482</t>
+          <t>1113071410</t>
         </is>
       </c>
       <c r="U253" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1965591482</t>
+          <t>https://m.place.naver.com/place/1113071410</t>
         </is>
       </c>
       <c r="V253" t="inlineStr">
@@ -23707,26 +23707,34 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>이용원</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>좋은인상이용원</t>
-        </is>
-      </c>
-      <c r="C254" t="inlineStr"/>
+          <t>에이엔헤어 수영광안점</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>qhrtnd_a@naver.com</t>
+        </is>
+      </c>
       <c r="D254" t="inlineStr"/>
-      <c r="E254" t="inlineStr"/>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>0507-1329-6675</t>
+        </is>
+      </c>
       <c r="F254" t="inlineStr"/>
       <c r="G254" t="inlineStr">
         <is>
-          <t>부산광역시 수영구 좌수영로83번길 28</t>
+          <t>부산광역시 수영구 호암로29번길 63 2층</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://www.instagram.com/a.nhair_official</t>
         </is>
       </c>
       <c r="I254" t="inlineStr">
@@ -23736,7 +23744,7 @@
       </c>
       <c r="J254" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K254" t="inlineStr">
@@ -23757,17 +23765,17 @@
       </c>
       <c r="O254" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P254" t="n">
-        <v>2</v>
+        <v>577</v>
       </c>
       <c r="Q254" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R254" t="n">
-        <v>2</v>
+        <v>582</v>
       </c>
       <c r="S254" t="inlineStr">
         <is>
@@ -23776,12 +23784,12 @@
       </c>
       <c r="T254" t="inlineStr">
         <is>
-          <t>1138097691</t>
+          <t>1211634766</t>
         </is>
       </c>
       <c r="U254" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1138097691</t>
+          <t>https://m.place.naver.com/place/1211634766</t>
         </is>
       </c>
       <c r="V254" t="inlineStr">
@@ -23793,34 +23801,30 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>이용원</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>빅가이바버샵</t>
-        </is>
-      </c>
-      <c r="C255" t="inlineStr">
-        <is>
-          <t>freehoo2@naver.com</t>
-        </is>
-      </c>
+          <t>헤어공간</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr"/>
       <c r="D255" t="inlineStr"/>
       <c r="E255" t="inlineStr">
         <is>
-          <t>0507-1321-6575</t>
+          <t>0507-1476-5573</t>
         </is>
       </c>
       <c r="F255" t="inlineStr"/>
       <c r="G255" t="inlineStr">
         <is>
-          <t>부산광역시 수영구 망미번영로52번길 39 1층 골목 첫번째 상가</t>
+          <t>부산광역시 수영구 수영로 776 센텀포레상가 2층 202-2</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/freehoo2</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I255" t="inlineStr">
@@ -23830,12 +23834,12 @@
       </c>
       <c r="J255" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K255" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L255" t="inlineStr">
@@ -23855,13 +23859,13 @@
         </is>
       </c>
       <c r="P255" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="Q255" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="R255" t="n">
-        <v>72</v>
+        <v>9</v>
       </c>
       <c r="S255" t="inlineStr">
         <is>
@@ -23870,12 +23874,12 @@
       </c>
       <c r="T255" t="inlineStr">
         <is>
-          <t>1033478003</t>
+          <t>1027368394</t>
         </is>
       </c>
       <c r="U255" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1033478003</t>
+          <t>https://m.place.naver.com/place/1027368394</t>
         </is>
       </c>
       <c r="V255" t="inlineStr">
@@ -23887,34 +23891,26 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>이용원</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>드라이빌 바버샵</t>
-        </is>
-      </c>
-      <c r="C256" t="inlineStr">
-        <is>
-          <t>dryville@naver.com</t>
-        </is>
-      </c>
+          <t>와와헤어</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr"/>
       <c r="D256" t="inlineStr"/>
-      <c r="E256" t="inlineStr">
-        <is>
-          <t>0507-1352-9061</t>
-        </is>
-      </c>
+      <c r="E256" t="inlineStr"/>
       <c r="F256" t="inlineStr"/>
       <c r="G256" t="inlineStr">
         <is>
-          <t>부산광역시 수영구 수영로394번길 23 1층</t>
+          <t>부산광역시 수영구 연수로264번길 24</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/dryville</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I256" t="inlineStr">
@@ -23924,12 +23920,12 @@
       </c>
       <c r="J256" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K256" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L256" t="inlineStr">
@@ -23945,17 +23941,17 @@
       </c>
       <c r="O256" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P256" t="n">
-        <v>166</v>
+        <v>5</v>
       </c>
       <c r="Q256" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="R256" t="n">
-        <v>177</v>
+        <v>5</v>
       </c>
       <c r="S256" t="inlineStr">
         <is>
@@ -23964,12 +23960,12 @@
       </c>
       <c r="T256" t="inlineStr">
         <is>
-          <t>2064471377</t>
+          <t>17052834</t>
         </is>
       </c>
       <c r="U256" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2064471377</t>
+          <t>https://m.place.naver.com/place/17052834</t>
         </is>
       </c>
       <c r="V256" t="inlineStr">
@@ -23981,30 +23977,34 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>이용원</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>나모 바버샵</t>
-        </is>
-      </c>
-      <c r="C257" t="inlineStr"/>
+          <t>라블룸</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>hpi6909@naver.com</t>
+        </is>
+      </c>
       <c r="D257" t="inlineStr"/>
       <c r="E257" t="inlineStr">
         <is>
-          <t>0507-1311-7302</t>
+          <t>0507-1325-2400</t>
         </is>
       </c>
       <c r="F257" t="inlineStr"/>
       <c r="G257" t="inlineStr">
         <is>
-          <t>부산광역시 수영구 남천바다로22번길 28 1층</t>
+          <t>부산광역시 수영구 남천동로 91 금호어울림비치상가 2층 202호 라블룸</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/namobarbershop/</t>
+          <t>https://blog.naver.com/hpi6909</t>
         </is>
       </c>
       <c r="I257" t="inlineStr">
@@ -24019,7 +24019,7 @@
       </c>
       <c r="K257" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L257" t="inlineStr">
@@ -24039,13 +24039,13 @@
         </is>
       </c>
       <c r="P257" t="n">
-        <v>1576</v>
+        <v>921</v>
       </c>
       <c r="Q257" t="n">
-        <v>343</v>
+        <v>20</v>
       </c>
       <c r="R257" t="n">
-        <v>1919</v>
+        <v>941</v>
       </c>
       <c r="S257" t="inlineStr">
         <is>
@@ -24054,12 +24054,12 @@
       </c>
       <c r="T257" t="inlineStr">
         <is>
-          <t>37672836</t>
+          <t>1252979443</t>
         </is>
       </c>
       <c r="U257" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37672836</t>
+          <t>https://m.place.naver.com/place/1252979443</t>
         </is>
       </c>
       <c r="V257" t="inlineStr">
@@ -24071,25 +24071,25 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>이용원</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>대성이용원</t>
+          <t>플로라헤어</t>
         </is>
       </c>
       <c r="C258" t="inlineStr"/>
       <c r="D258" t="inlineStr"/>
       <c r="E258" t="inlineStr">
         <is>
-          <t>051-753-4797</t>
+          <t>051-752-2360</t>
         </is>
       </c>
       <c r="F258" t="inlineStr"/>
       <c r="G258" t="inlineStr">
         <is>
-          <t>부산광역시 수영구 수미로50번길 37-1</t>
+          <t>부산광역시 수영구 과정로 89 1층플로라헤어</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
@@ -24129,13 +24129,13 @@
         </is>
       </c>
       <c r="P258" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="Q258" t="n">
         <v>0</v>
       </c>
       <c r="R258" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="S258" t="inlineStr">
         <is>
@@ -24144,12 +24144,12 @@
       </c>
       <c r="T258" t="inlineStr">
         <is>
-          <t>37981888</t>
+          <t>1024438038</t>
         </is>
       </c>
       <c r="U258" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/37981888</t>
+          <t>https://m.place.naver.com/place/1024438038</t>
         </is>
       </c>
       <c r="V258" t="inlineStr">
@@ -24161,29 +24161,29 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>인테리어디자인</t>
+          <t>미용실</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>페니디자인</t>
+          <t>강찬숙헤어스타일</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>mond0120@naver.com</t>
+          <t>mingsday325@naver.com</t>
         </is>
       </c>
       <c r="D259" t="inlineStr"/>
       <c r="E259" t="inlineStr">
         <is>
-          <t>0507-1488-1499</t>
+          <t>051-752-7109</t>
         </is>
       </c>
       <c r="F259" t="inlineStr"/>
       <c r="G259" t="inlineStr">
         <is>
-          <t>부산광역시 수영구 광안로61번길 12 페니디자인</t>
+          <t>부산광역시 수영구 연수로357번길 26</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
@@ -24223,10 +24223,10 @@
         </is>
       </c>
       <c r="P259" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q259" t="n">
         <v>0</v>
-      </c>
-      <c r="Q259" t="n">
-        <v>3</v>
       </c>
       <c r="R259" t="n">
         <v>3</v>
@@ -24238,15 +24238,6749 @@
       </c>
       <c r="T259" t="inlineStr">
         <is>
+          <t>19660855</t>
+        </is>
+      </c>
+      <c r="U259" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/19660855</t>
+        </is>
+      </c>
+      <c r="V259" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>미용실</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>동양컷트미용실</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr"/>
+      <c r="D260" t="inlineStr"/>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>051-754-9638</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr"/>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>부산광역시 수영구 수영로705번길 37-14</t>
+        </is>
+      </c>
+      <c r="H260" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I260" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J260" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L260" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M260" t="inlineStr"/>
+      <c r="N260" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O260" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P260" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q260" t="n">
+        <v>0</v>
+      </c>
+      <c r="R260" t="n">
+        <v>1</v>
+      </c>
+      <c r="S260" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T260" t="inlineStr">
+        <is>
+          <t>16677508</t>
+        </is>
+      </c>
+      <c r="U260" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/16677508</t>
+        </is>
+      </c>
+      <c r="V260" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>미용실</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>조은날헤어샵</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>allzzangz@naver.com</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr"/>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>0507-1477-7976</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr"/>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>부산광역시 수영구 과정로41번길 65 1층 조은날헤어샵</t>
+        </is>
+      </c>
+      <c r="H261" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I261" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J261" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K261" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L261" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M261" t="inlineStr"/>
+      <c r="N261" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O261" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P261" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q261" t="n">
+        <v>0</v>
+      </c>
+      <c r="R261" t="n">
+        <v>3</v>
+      </c>
+      <c r="S261" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T261" t="inlineStr">
+        <is>
+          <t>1183859997</t>
+        </is>
+      </c>
+      <c r="U261" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1183859997</t>
+        </is>
+      </c>
+      <c r="V261" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>미용실</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>세림헤어샵</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr"/>
+      <c r="D262" t="inlineStr"/>
+      <c r="E262" t="inlineStr"/>
+      <c r="F262" t="inlineStr"/>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>부산광역시 수영구 수영성로8번길 4</t>
+        </is>
+      </c>
+      <c r="H262" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I262" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J262" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K262" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L262" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M262" t="inlineStr"/>
+      <c r="N262" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O262" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P262" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q262" t="n">
+        <v>0</v>
+      </c>
+      <c r="R262" t="n">
+        <v>2</v>
+      </c>
+      <c r="S262" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T262" t="inlineStr">
+        <is>
+          <t>1381659608</t>
+        </is>
+      </c>
+      <c r="U262" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1381659608</t>
+        </is>
+      </c>
+      <c r="V262" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>미용실</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>박유주헤어피부샵</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>bakbht@naver.com</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr"/>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>051-756-5341</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr"/>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>부산광역시 수영구 광안해변로277번길 11</t>
+        </is>
+      </c>
+      <c r="H263" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I263" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J263" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K263" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L263" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M263" t="inlineStr"/>
+      <c r="N263" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O263" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P263" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q263" t="n">
+        <v>0</v>
+      </c>
+      <c r="R263" t="n">
+        <v>3</v>
+      </c>
+      <c r="S263" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T263" t="inlineStr">
+        <is>
+          <t>16683621</t>
+        </is>
+      </c>
+      <c r="U263" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/16683621</t>
+        </is>
+      </c>
+      <c r="V263" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>미용실</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>팟찌헤어</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>chainch@naver.com</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr"/>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>051-753-7978</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr"/>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>부산광역시 수영구 과정로41번길 16</t>
+        </is>
+      </c>
+      <c r="H264" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I264" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J264" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L264" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M264" t="inlineStr"/>
+      <c r="N264" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O264" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P264" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q264" t="n">
+        <v>0</v>
+      </c>
+      <c r="R264" t="n">
+        <v>10</v>
+      </c>
+      <c r="S264" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T264" t="inlineStr">
+        <is>
+          <t>17054058</t>
+        </is>
+      </c>
+      <c r="U264" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/17054058</t>
+        </is>
+      </c>
+      <c r="V264" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>미용실</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>드라포레 수영점</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>lkmforet@naver.com</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr"/>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>0507-1442-5755</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr"/>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>부산광역시 수영구 무학로63번길 142 센텀비스타동원 2차상가 2층</t>
+        </is>
+      </c>
+      <c r="H265" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/delaforet_suyeong</t>
+        </is>
+      </c>
+      <c r="I265" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J265" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K265" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L265" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M265" t="inlineStr"/>
+      <c r="N265" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O265" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P265" t="n">
+        <v>10189</v>
+      </c>
+      <c r="Q265" t="n">
+        <v>440</v>
+      </c>
+      <c r="R265" t="n">
+        <v>10629</v>
+      </c>
+      <c r="S265" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T265" t="inlineStr">
+        <is>
+          <t>445088382</t>
+        </is>
+      </c>
+      <c r="U265" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/445088382</t>
+        </is>
+      </c>
+      <c r="V265" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>남성전문미용실</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>코지맨즈</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>zinu_rh@naver.com</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr"/>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>0507-1492-2387</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr"/>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>부산광역시 수영구 수영로510번길 7 2층</t>
+        </is>
+      </c>
+      <c r="H266" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/cozymens_/</t>
+        </is>
+      </c>
+      <c r="I266" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J266" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K266" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L266" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M266" t="inlineStr"/>
+      <c r="N266" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O266" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P266" t="n">
+        <v>274</v>
+      </c>
+      <c r="Q266" t="n">
+        <v>33</v>
+      </c>
+      <c r="R266" t="n">
+        <v>307</v>
+      </c>
+      <c r="S266" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T266" t="inlineStr">
+        <is>
+          <t>1408881297</t>
+        </is>
+      </c>
+      <c r="U266" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1408881297</t>
+        </is>
+      </c>
+      <c r="V266" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>미용실</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>휴디헤어 남천점</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>hyudi_hair@naver.com</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr"/>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>0507-1435-0489</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr"/>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>부산광역시 수영구 수영로464번길 9 준정빌딩 2층 휴디헤어 남천점</t>
+        </is>
+      </c>
+      <c r="H267" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/hyu.di_hair</t>
+        </is>
+      </c>
+      <c r="I267" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J267" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K267" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L267" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M267" t="inlineStr"/>
+      <c r="N267" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O267" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P267" t="n">
+        <v>2274</v>
+      </c>
+      <c r="Q267" t="n">
+        <v>178</v>
+      </c>
+      <c r="R267" t="n">
+        <v>2452</v>
+      </c>
+      <c r="S267" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T267" t="inlineStr">
+        <is>
+          <t>1080340473</t>
+        </is>
+      </c>
+      <c r="U267" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1080340473</t>
+        </is>
+      </c>
+      <c r="V267" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>미용실</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>망미동미용실</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>mora2200@naver.com</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr"/>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>0507-1389-2026</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr"/>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>부산광역시 수영구 과정로 35 1층 망미동미용실</t>
+        </is>
+      </c>
+      <c r="H268" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/mora2200</t>
+        </is>
+      </c>
+      <c r="I268" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J268" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K268" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L268" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M268" t="inlineStr"/>
+      <c r="N268" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O268" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P268" t="n">
+        <v>126</v>
+      </c>
+      <c r="Q268" t="n">
+        <v>1</v>
+      </c>
+      <c r="R268" t="n">
+        <v>127</v>
+      </c>
+      <c r="S268" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T268" t="inlineStr">
+        <is>
+          <t>1607458723</t>
+        </is>
+      </c>
+      <c r="U268" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1607458723</t>
+        </is>
+      </c>
+      <c r="V268" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>미용실</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>채현헤어살롱</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>nsh1211@naver.com</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr"/>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>0507-0076-0498</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr"/>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>부산광역시 수영구 연수로370번길 20-2 채현헤어살롱 1층</t>
+        </is>
+      </c>
+      <c r="H269" t="inlineStr">
+        <is>
+          <t>https://www.keyweb.kr/detail.php?number=998</t>
+        </is>
+      </c>
+      <c r="I269" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J269" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K269" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L269" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M269" t="inlineStr"/>
+      <c r="N269" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O269" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P269" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q269" t="n">
+        <v>15</v>
+      </c>
+      <c r="R269" t="n">
+        <v>25</v>
+      </c>
+      <c r="S269" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T269" t="inlineStr">
+        <is>
+          <t>37749820</t>
+        </is>
+      </c>
+      <c r="U269" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/37749820</t>
+        </is>
+      </c>
+      <c r="V269" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>미용실</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>헤어바이지율</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr"/>
+      <c r="D270" t="inlineStr"/>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>051-754-7288</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr"/>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>부산광역시 수영구 연수로315번길 24</t>
+        </is>
+      </c>
+      <c r="H270" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I270" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J270" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K270" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L270" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M270" t="inlineStr"/>
+      <c r="N270" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O270" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P270" t="n">
+        <v>29</v>
+      </c>
+      <c r="Q270" t="n">
+        <v>0</v>
+      </c>
+      <c r="R270" t="n">
+        <v>29</v>
+      </c>
+      <c r="S270" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T270" t="inlineStr">
+        <is>
+          <t>1646161935</t>
+        </is>
+      </c>
+      <c r="U270" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1646161935</t>
+        </is>
+      </c>
+      <c r="V270" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>미용실</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>정머리방</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>js5040212@naver.com</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr"/>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>051-756-3036</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr"/>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>부산광역시 수영구 과정로41번길 30</t>
+        </is>
+      </c>
+      <c r="H271" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I271" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J271" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K271" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L271" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M271" t="inlineStr"/>
+      <c r="N271" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O271" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P271" t="n">
+        <v>24</v>
+      </c>
+      <c r="Q271" t="n">
+        <v>0</v>
+      </c>
+      <c r="R271" t="n">
+        <v>24</v>
+      </c>
+      <c r="S271" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T271" t="inlineStr">
+        <is>
+          <t>17050599</t>
+        </is>
+      </c>
+      <c r="U271" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/17050599</t>
+        </is>
+      </c>
+      <c r="V271" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>미용실</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>자르다헤어&amp;네일은</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>n_ksm@naver.com</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr"/>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>051-622-1227</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr"/>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>부산광역시 수영구 수영로408번길 29 1층자르다헤어&amp;네일은</t>
+        </is>
+      </c>
+      <c r="H272" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I272" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J272" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K272" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L272" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M272" t="inlineStr"/>
+      <c r="N272" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O272" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P272" t="n">
+        <v>31</v>
+      </c>
+      <c r="Q272" t="n">
+        <v>3</v>
+      </c>
+      <c r="R272" t="n">
+        <v>34</v>
+      </c>
+      <c r="S272" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T272" t="inlineStr">
+        <is>
+          <t>37977189</t>
+        </is>
+      </c>
+      <c r="U272" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/37977189</t>
+        </is>
+      </c>
+      <c r="V272" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>미용실</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>테리아미용실</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>gmlcks0728@naver.com</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr"/>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>0507-1339-4661</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr"/>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>부산광역시 수영구 연수로 262 1층 미용실</t>
+        </is>
+      </c>
+      <c r="H273" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/kyou2799</t>
+        </is>
+      </c>
+      <c r="I273" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J273" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K273" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L273" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M273" t="inlineStr"/>
+      <c r="N273" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O273" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P273" t="n">
+        <v>104</v>
+      </c>
+      <c r="Q273" t="n">
+        <v>2</v>
+      </c>
+      <c r="R273" t="n">
+        <v>106</v>
+      </c>
+      <c r="S273" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T273" t="inlineStr">
+        <is>
+          <t>1009515709</t>
+        </is>
+      </c>
+      <c r="U273" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1009515709</t>
+        </is>
+      </c>
+      <c r="V273" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>미용실</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>늘. 봄날</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>bomnalhair23@naver.com</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr"/>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>0507-1414-7523</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr"/>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>부산광역시 수영구 광안해변로15번길 54 상가12호 늘,봄날 hairsalon</t>
+        </is>
+      </c>
+      <c r="H274" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/bomnalhair23</t>
+        </is>
+      </c>
+      <c r="I274" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J274" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K274" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L274" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M274" t="inlineStr"/>
+      <c r="N274" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O274" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P274" t="n">
+        <v>88</v>
+      </c>
+      <c r="Q274" t="n">
+        <v>11</v>
+      </c>
+      <c r="R274" t="n">
+        <v>99</v>
+      </c>
+      <c r="S274" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T274" t="inlineStr">
+        <is>
+          <t>1544084483</t>
+        </is>
+      </c>
+      <c r="U274" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1544084483</t>
+        </is>
+      </c>
+      <c r="V274" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>미용실</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>바이몬트</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>govlqufsla@naver.com</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr"/>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>0507-1325-0203</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr"/>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>부산광역시 수영구 광안해변로294번길 36 2층</t>
+        </is>
+      </c>
+      <c r="H275" t="inlineStr">
+        <is>
+          <t>https://pf.kakao.com/_aqxlZn</t>
+        </is>
+      </c>
+      <c r="I275" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J275" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K275" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L275" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M275" t="inlineStr"/>
+      <c r="N275" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O275" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P275" t="n">
+        <v>1186</v>
+      </c>
+      <c r="Q275" t="n">
+        <v>49</v>
+      </c>
+      <c r="R275" t="n">
+        <v>1235</v>
+      </c>
+      <c r="S275" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T275" t="inlineStr">
+        <is>
+          <t>1673786017</t>
+        </is>
+      </c>
+      <c r="U275" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1673786017</t>
+        </is>
+      </c>
+      <c r="V275" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>미용실</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>모완10헤어 수영센텀점</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>policelover12@naver.com</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr"/>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>0507-1468-0604</t>
+        </is>
+      </c>
+      <c r="F276" t="inlineStr"/>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>부산광역시 수영구 수미로36번길 4 1층 모완10헤어 수영센텀점</t>
+        </is>
+      </c>
+      <c r="H276" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/shjy0404</t>
+        </is>
+      </c>
+      <c r="I276" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J276" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K276" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L276" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M276" t="inlineStr"/>
+      <c r="N276" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O276" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P276" t="n">
+        <v>48</v>
+      </c>
+      <c r="Q276" t="n">
+        <v>2</v>
+      </c>
+      <c r="R276" t="n">
+        <v>50</v>
+      </c>
+      <c r="S276" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T276" t="inlineStr">
+        <is>
+          <t>383430557</t>
+        </is>
+      </c>
+      <c r="U276" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/383430557</t>
+        </is>
+      </c>
+      <c r="V276" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>남성전문미용실</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>신싸롱</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>ksjice@naver.com</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr"/>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>070-8888-2882</t>
+        </is>
+      </c>
+      <c r="F277" t="inlineStr"/>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>부산광역시 수영구 남천동로 33</t>
+        </is>
+      </c>
+      <c r="H277" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I277" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J277" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K277" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L277" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M277" t="inlineStr"/>
+      <c r="N277" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O277" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P277" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q277" t="n">
+        <v>0</v>
+      </c>
+      <c r="R277" t="n">
+        <v>17</v>
+      </c>
+      <c r="S277" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T277" t="inlineStr">
+        <is>
+          <t>1260271697</t>
+        </is>
+      </c>
+      <c r="U277" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1260271697</t>
+        </is>
+      </c>
+      <c r="V277" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>미용실</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>금빛살롱</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>twinkle_points@naver.com</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr"/>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>0507-1379-8873</t>
+        </is>
+      </c>
+      <c r="F278" t="inlineStr"/>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>부산광역시 수영구 광서로 17-1 금빛살롱</t>
+        </is>
+      </c>
+      <c r="H278" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/han.teacher</t>
+        </is>
+      </c>
+      <c r="I278" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J278" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K278" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L278" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M278" t="inlineStr"/>
+      <c r="N278" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O278" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P278" t="n">
+        <v>145</v>
+      </c>
+      <c r="Q278" t="n">
+        <v>28</v>
+      </c>
+      <c r="R278" t="n">
+        <v>173</v>
+      </c>
+      <c r="S278" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T278" t="inlineStr">
+        <is>
+          <t>1576081649</t>
+        </is>
+      </c>
+      <c r="U278" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1576081649</t>
+        </is>
+      </c>
+      <c r="V278" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>미용실</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>하이플랜트 광안</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr"/>
+      <c r="D279" t="inlineStr"/>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>0507-1376-7769</t>
+        </is>
+      </c>
+      <c r="F279" t="inlineStr"/>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>부산광역시 수영구 남천바다로9번길 4 2층</t>
+        </is>
+      </c>
+      <c r="H279" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/hp2_daeun</t>
+        </is>
+      </c>
+      <c r="I279" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J279" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K279" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L279" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M279" t="inlineStr"/>
+      <c r="N279" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O279" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P279" t="n">
+        <v>616</v>
+      </c>
+      <c r="Q279" t="n">
+        <v>12</v>
+      </c>
+      <c r="R279" t="n">
+        <v>628</v>
+      </c>
+      <c r="S279" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T279" t="inlineStr">
+        <is>
+          <t>1476820865</t>
+        </is>
+      </c>
+      <c r="U279" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1476820865</t>
+        </is>
+      </c>
+      <c r="V279" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>미용실</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>이양숙헤어숍</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>hjstylemm@naver.com</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr"/>
+      <c r="E280" t="inlineStr"/>
+      <c r="F280" t="inlineStr"/>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>부산광역시 수영구 민락본동로31번길 51 왕신빌라</t>
+        </is>
+      </c>
+      <c r="H280" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I280" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J280" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K280" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L280" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M280" t="inlineStr"/>
+      <c r="N280" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O280" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P280" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q280" t="n">
+        <v>0</v>
+      </c>
+      <c r="R280" t="n">
+        <v>0</v>
+      </c>
+      <c r="S280" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T280" t="inlineStr">
+        <is>
+          <t>1053173574</t>
+        </is>
+      </c>
+      <c r="U280" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1053173574</t>
+        </is>
+      </c>
+      <c r="V280" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>미용실</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>하유진헤어</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>qkrwldo01@naver.com</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr"/>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>0507-1318-5494</t>
+        </is>
+      </c>
+      <c r="F281" t="inlineStr"/>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>부산광역시 수영구 광안해변로 418 상가동 3층 301호</t>
+        </is>
+      </c>
+      <c r="H281" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I281" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J281" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K281" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L281" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M281" t="inlineStr"/>
+      <c r="N281" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O281" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P281" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q281" t="n">
+        <v>0</v>
+      </c>
+      <c r="R281" t="n">
+        <v>4</v>
+      </c>
+      <c r="S281" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T281" t="inlineStr">
+        <is>
+          <t>1057150079</t>
+        </is>
+      </c>
+      <c r="U281" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1057150079</t>
+        </is>
+      </c>
+      <c r="V281" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>미용실</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>복도미용실</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>skagudgh88@naver.com</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr"/>
+      <c r="E282" t="inlineStr"/>
+      <c r="F282" t="inlineStr"/>
+      <c r="G282" t="inlineStr">
+        <is>
+          <t>부산광역시 수영구 수영성로 16</t>
+        </is>
+      </c>
+      <c r="H282" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I282" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J282" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K282" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L282" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M282" t="inlineStr"/>
+      <c r="N282" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O282" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P282" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q282" t="n">
+        <v>0</v>
+      </c>
+      <c r="R282" t="n">
+        <v>0</v>
+      </c>
+      <c r="S282" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T282" t="inlineStr">
+        <is>
+          <t>1595225172</t>
+        </is>
+      </c>
+      <c r="U282" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1595225172</t>
+        </is>
+      </c>
+      <c r="V282" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>미용실</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>예원헤어룸</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>iapplev2@naver.com</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr"/>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>0507-1363-9943</t>
+        </is>
+      </c>
+      <c r="F283" t="inlineStr"/>
+      <c r="G283" t="inlineStr">
+        <is>
+          <t>부산광역시 수영구 수영로 641 101동 106호</t>
+        </is>
+      </c>
+      <c r="H283" t="inlineStr">
+        <is>
+          <t>http://instagram.com/yewon_HairRoom</t>
+        </is>
+      </c>
+      <c r="I283" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J283" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K283" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L283" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M283" t="inlineStr"/>
+      <c r="N283" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O283" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P283" t="n">
+        <v>1113</v>
+      </c>
+      <c r="Q283" t="n">
+        <v>9</v>
+      </c>
+      <c r="R283" t="n">
+        <v>1122</v>
+      </c>
+      <c r="S283" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T283" t="inlineStr">
+        <is>
+          <t>1419554830</t>
+        </is>
+      </c>
+      <c r="U283" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1419554830</t>
+        </is>
+      </c>
+      <c r="V283" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>미용실</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>코코인헤어</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>lailaixien@naver.com</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr"/>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>0507-1397-7455</t>
+        </is>
+      </c>
+      <c r="F284" t="inlineStr"/>
+      <c r="G284" t="inlineStr">
+        <is>
+          <t>부산광역시 수영구 수영로725번길 48 텐퍼센트커피 2층(팔도시장입구)</t>
+        </is>
+      </c>
+      <c r="H284" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/cocoin_hair</t>
+        </is>
+      </c>
+      <c r="I284" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J284" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K284" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L284" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M284" t="inlineStr"/>
+      <c r="N284" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O284" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P284" t="n">
+        <v>167</v>
+      </c>
+      <c r="Q284" t="n">
+        <v>0</v>
+      </c>
+      <c r="R284" t="n">
+        <v>167</v>
+      </c>
+      <c r="S284" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T284" t="inlineStr">
+        <is>
+          <t>1702054524</t>
+        </is>
+      </c>
+      <c r="U284" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1702054524</t>
+        </is>
+      </c>
+      <c r="V284" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>미용실</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>살롱세나</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr"/>
+      <c r="D285" t="inlineStr"/>
+      <c r="E285" t="inlineStr"/>
+      <c r="F285" t="inlineStr"/>
+      <c r="G285" t="inlineStr">
+        <is>
+          <t>부산광역시 수영구 과정로79번길 2 1층</t>
+        </is>
+      </c>
+      <c r="H285" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I285" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J285" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K285" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L285" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M285" t="inlineStr"/>
+      <c r="N285" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O285" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P285" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q285" t="n">
+        <v>0</v>
+      </c>
+      <c r="R285" t="n">
+        <v>9</v>
+      </c>
+      <c r="S285" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T285" t="inlineStr">
+        <is>
+          <t>1607412490</t>
+        </is>
+      </c>
+      <c r="U285" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1607412490</t>
+        </is>
+      </c>
+      <c r="V285" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>미용실</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>빈오드</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr"/>
+      <c r="D286" t="inlineStr"/>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>0507-1496-0691</t>
+        </is>
+      </c>
+      <c r="F286" t="inlineStr"/>
+      <c r="G286" t="inlineStr">
+        <is>
+          <t>부산광역시 수영구 수영로536번길 31 2층</t>
+        </is>
+      </c>
+      <c r="H286" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/binbin.st</t>
+        </is>
+      </c>
+      <c r="I286" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J286" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K286" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L286" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M286" t="inlineStr"/>
+      <c r="N286" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O286" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P286" t="n">
+        <v>125</v>
+      </c>
+      <c r="Q286" t="n">
+        <v>4</v>
+      </c>
+      <c r="R286" t="n">
+        <v>129</v>
+      </c>
+      <c r="S286" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T286" t="inlineStr">
+        <is>
+          <t>1514785707</t>
+        </is>
+      </c>
+      <c r="U286" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1514785707</t>
+        </is>
+      </c>
+      <c r="V286" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>미용실</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>유아크헤어 수영광안점</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr"/>
+      <c r="D287" t="inlineStr"/>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>051-913-5666</t>
+        </is>
+      </c>
+      <c r="F287" t="inlineStr"/>
+      <c r="G287" t="inlineStr">
+        <is>
+          <t>부산광역시 수영구 광남로 120 2층</t>
+        </is>
+      </c>
+      <c r="H287" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/u.arc_gwanganri_officail/</t>
+        </is>
+      </c>
+      <c r="I287" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J287" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K287" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L287" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M287" t="inlineStr"/>
+      <c r="N287" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O287" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P287" t="n">
+        <v>1184</v>
+      </c>
+      <c r="Q287" t="n">
+        <v>1603</v>
+      </c>
+      <c r="R287" t="n">
+        <v>2787</v>
+      </c>
+      <c r="S287" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T287" t="inlineStr">
+        <is>
+          <t>1556082746</t>
+        </is>
+      </c>
+      <c r="U287" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1556082746</t>
+        </is>
+      </c>
+      <c r="V287" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>미용실</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>오운미헤어</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>jyl0904@naver.com</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr"/>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>0507-1344-5584</t>
+        </is>
+      </c>
+      <c r="F288" t="inlineStr"/>
+      <c r="G288" t="inlineStr">
+        <is>
+          <t>부산광역시 수영구 장대골로7번길 42 103호</t>
+        </is>
+      </c>
+      <c r="H288" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/soyou_own?igsh=enBjc3I3ZjZybXFu</t>
+        </is>
+      </c>
+      <c r="I288" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J288" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K288" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L288" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M288" t="inlineStr"/>
+      <c r="N288" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O288" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P288" t="n">
+        <v>103</v>
+      </c>
+      <c r="Q288" t="n">
+        <v>190</v>
+      </c>
+      <c r="R288" t="n">
+        <v>293</v>
+      </c>
+      <c r="S288" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T288" t="inlineStr">
+        <is>
+          <t>2004087651</t>
+        </is>
+      </c>
+      <c r="U288" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2004087651</t>
+        </is>
+      </c>
+      <c r="V288" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>미용실</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>이영희헤어</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr"/>
+      <c r="D289" t="inlineStr"/>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>0507-1378-4258</t>
+        </is>
+      </c>
+      <c r="F289" t="inlineStr"/>
+      <c r="G289" t="inlineStr">
+        <is>
+          <t>부산광역시 수영구 수영로 754 103호</t>
+        </is>
+      </c>
+      <c r="H289" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I289" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J289" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K289" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L289" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M289" t="inlineStr"/>
+      <c r="N289" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O289" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P289" t="n">
+        <v>73</v>
+      </c>
+      <c r="Q289" t="n">
+        <v>0</v>
+      </c>
+      <c r="R289" t="n">
+        <v>73</v>
+      </c>
+      <c r="S289" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T289" t="inlineStr">
+        <is>
+          <t>1225520890</t>
+        </is>
+      </c>
+      <c r="U289" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1225520890</t>
+        </is>
+      </c>
+      <c r="V289" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>미용실</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>더봄헤어</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>plaire1113@naver.com</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr"/>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>0507-1431-5332</t>
+        </is>
+      </c>
+      <c r="F290" t="inlineStr"/>
+      <c r="G290" t="inlineStr">
+        <is>
+          <t>부산광역시 수영구 수미로58번길 18-2 1층</t>
+        </is>
+      </c>
+      <c r="H290" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I290" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J290" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K290" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L290" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M290" t="inlineStr"/>
+      <c r="N290" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O290" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P290" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q290" t="n">
+        <v>0</v>
+      </c>
+      <c r="R290" t="n">
+        <v>8</v>
+      </c>
+      <c r="S290" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T290" t="inlineStr">
+        <is>
+          <t>1687577040</t>
+        </is>
+      </c>
+      <c r="U290" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1687577040</t>
+        </is>
+      </c>
+      <c r="V290" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>미용실</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>이지숙헤어</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>tnguddmswl@naver.com</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr"/>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>051-623-1213</t>
+        </is>
+      </c>
+      <c r="F291" t="inlineStr"/>
+      <c r="G291" t="inlineStr">
+        <is>
+          <t>부산광역시 수영구 광남로48번길 16</t>
+        </is>
+      </c>
+      <c r="H291" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I291" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J291" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K291" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L291" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M291" t="inlineStr"/>
+      <c r="N291" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O291" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P291" t="n">
+        <v>38</v>
+      </c>
+      <c r="Q291" t="n">
+        <v>0</v>
+      </c>
+      <c r="R291" t="n">
+        <v>38</v>
+      </c>
+      <c r="S291" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T291" t="inlineStr">
+        <is>
+          <t>37978105</t>
+        </is>
+      </c>
+      <c r="U291" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/37978105</t>
+        </is>
+      </c>
+      <c r="V291" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>미용실</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>비베아</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>hyxx_nii@naver.com</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr"/>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>0507-1432-3581</t>
+        </is>
+      </c>
+      <c r="F292" t="inlineStr"/>
+      <c r="G292" t="inlineStr">
+        <is>
+          <t>부산광역시 수영구 수영로 571 3층</t>
+        </is>
+      </c>
+      <c r="H292" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/vivea_daily/</t>
+        </is>
+      </c>
+      <c r="I292" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J292" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K292" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L292" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M292" t="inlineStr"/>
+      <c r="N292" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O292" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P292" t="n">
+        <v>131</v>
+      </c>
+      <c r="Q292" t="n">
+        <v>184</v>
+      </c>
+      <c r="R292" t="n">
+        <v>315</v>
+      </c>
+      <c r="S292" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T292" t="inlineStr">
+        <is>
+          <t>2004083271</t>
+        </is>
+      </c>
+      <c r="U292" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2004083271</t>
+        </is>
+      </c>
+      <c r="V292" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>미용실</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>누아브헤어</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>hyeonl_j@naver.com</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr"/>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>0507-1397-7432</t>
+        </is>
+      </c>
+      <c r="F293" t="inlineStr"/>
+      <c r="G293" t="inlineStr">
+        <is>
+          <t>부산광역시 수영구 무학로63번길 142 센텀비스타동원2차상가 401동 115호 1층 누아브헤어</t>
+        </is>
+      </c>
+      <c r="H293" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/hyeonl_j</t>
+        </is>
+      </c>
+      <c r="I293" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J293" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K293" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L293" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M293" t="inlineStr"/>
+      <c r="N293" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O293" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P293" t="n">
+        <v>28</v>
+      </c>
+      <c r="Q293" t="n">
+        <v>2</v>
+      </c>
+      <c r="R293" t="n">
+        <v>30</v>
+      </c>
+      <c r="S293" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T293" t="inlineStr">
+        <is>
+          <t>2061852099</t>
+        </is>
+      </c>
+      <c r="U293" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2061852099</t>
+        </is>
+      </c>
+      <c r="V293" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>미용실</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>수아헤어</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>youngokjoy@naver.com</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr"/>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>070-4525-9909</t>
+        </is>
+      </c>
+      <c r="F294" t="inlineStr"/>
+      <c r="G294" t="inlineStr">
+        <is>
+          <t>부산광역시 수영구 수영로741번길 12 현대종합상가 208호</t>
+        </is>
+      </c>
+      <c r="H294" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/sua_hair_head_spa_suyeong</t>
+        </is>
+      </c>
+      <c r="I294" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J294" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K294" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L294" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M294" t="inlineStr"/>
+      <c r="N294" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O294" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P294" t="n">
+        <v>72</v>
+      </c>
+      <c r="Q294" t="n">
+        <v>142</v>
+      </c>
+      <c r="R294" t="n">
+        <v>214</v>
+      </c>
+      <c r="S294" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T294" t="inlineStr">
+        <is>
+          <t>727972507</t>
+        </is>
+      </c>
+      <c r="U294" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/727972507</t>
+        </is>
+      </c>
+      <c r="V294" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>미용실</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>류연선 헤어뷰티</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>hjstylemm@naver.com</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr"/>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>051-759-9908</t>
+        </is>
+      </c>
+      <c r="F295" t="inlineStr"/>
+      <c r="G295" t="inlineStr">
+        <is>
+          <t>부산광역시 수영구 연수로415번길 28</t>
+        </is>
+      </c>
+      <c r="H295" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I295" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J295" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K295" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L295" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M295" t="inlineStr"/>
+      <c r="N295" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O295" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P295" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q295" t="n">
+        <v>0</v>
+      </c>
+      <c r="R295" t="n">
+        <v>0</v>
+      </c>
+      <c r="S295" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T295" t="inlineStr">
+        <is>
+          <t>1629318500</t>
+        </is>
+      </c>
+      <c r="U295" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1629318500</t>
+        </is>
+      </c>
+      <c r="V295" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>미용실</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>은혜미용실</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr"/>
+      <c r="D296" t="inlineStr"/>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>051-627-3537</t>
+        </is>
+      </c>
+      <c r="F296" t="inlineStr"/>
+      <c r="G296" t="inlineStr">
+        <is>
+          <t>부산광역시 수영구 남천동로10번길 56 은혜미용실</t>
+        </is>
+      </c>
+      <c r="H296" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I296" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J296" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K296" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L296" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M296" t="inlineStr"/>
+      <c r="N296" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O296" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P296" t="n">
+        <v>47</v>
+      </c>
+      <c r="Q296" t="n">
+        <v>0</v>
+      </c>
+      <c r="R296" t="n">
+        <v>47</v>
+      </c>
+      <c r="S296" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T296" t="inlineStr">
+        <is>
+          <t>1769649827</t>
+        </is>
+      </c>
+      <c r="U296" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1769649827</t>
+        </is>
+      </c>
+      <c r="V296" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>미용실</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>윤헤어</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>yoonhairsalon@naver.com</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr"/>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>051-710-1177</t>
+        </is>
+      </c>
+      <c r="F297" t="inlineStr"/>
+      <c r="G297" t="inlineStr">
+        <is>
+          <t>부산광역시 수영구 민락로6번길 29 1층 윤헤어</t>
+        </is>
+      </c>
+      <c r="H297" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/yoonhairsalon</t>
+        </is>
+      </c>
+      <c r="I297" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J297" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K297" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L297" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M297" t="inlineStr"/>
+      <c r="N297" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O297" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P297" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q297" t="n">
+        <v>0</v>
+      </c>
+      <c r="R297" t="n">
+        <v>9</v>
+      </c>
+      <c r="S297" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T297" t="inlineStr">
+        <is>
+          <t>1350474930</t>
+        </is>
+      </c>
+      <c r="U297" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1350474930</t>
+        </is>
+      </c>
+      <c r="V297" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>미용실</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>라본헤어 부산센텀점</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>anri0708@naver.com</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr"/>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>0507-1307-8868</t>
+        </is>
+      </c>
+      <c r="F298" t="inlineStr"/>
+      <c r="G298" t="inlineStr">
+        <is>
+          <t>부산광역시 수영구 수영로 646 (광안동)</t>
+        </is>
+      </c>
+      <c r="H298" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/anri0708</t>
+        </is>
+      </c>
+      <c r="I298" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J298" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K298" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L298" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M298" t="inlineStr"/>
+      <c r="N298" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O298" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P298" t="n">
+        <v>1463</v>
+      </c>
+      <c r="Q298" t="n">
+        <v>182</v>
+      </c>
+      <c r="R298" t="n">
+        <v>1645</v>
+      </c>
+      <c r="S298" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T298" t="inlineStr">
+        <is>
+          <t>1801201877</t>
+        </is>
+      </c>
+      <c r="U298" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1801201877</t>
+        </is>
+      </c>
+      <c r="V298" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>미용실</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>킴스헤어</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>wnepd@naver.com</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr"/>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>0507-1315-2689</t>
+        </is>
+      </c>
+      <c r="F299" t="inlineStr"/>
+      <c r="G299" t="inlineStr">
+        <is>
+          <t>부산광역시 수영구 민락로6번길 46-2 1층 킴스헤어</t>
+        </is>
+      </c>
+      <c r="H299" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I299" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J299" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K299" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L299" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M299" t="inlineStr"/>
+      <c r="N299" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O299" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P299" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q299" t="n">
+        <v>0</v>
+      </c>
+      <c r="R299" t="n">
+        <v>2</v>
+      </c>
+      <c r="S299" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T299" t="inlineStr">
+        <is>
+          <t>2032676534</t>
+        </is>
+      </c>
+      <c r="U299" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2032676534</t>
+        </is>
+      </c>
+      <c r="V299" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>반려동물미용</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>도그리썸애견미용실</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>2001125064@naver.com</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr"/>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>051-753-6545</t>
+        </is>
+      </c>
+      <c r="F300" t="inlineStr"/>
+      <c r="G300" t="inlineStr">
+        <is>
+          <t>부산광역시 수영구 수영로652번길 72 1층</t>
+        </is>
+      </c>
+      <c r="H300" t="inlineStr">
+        <is>
+          <t>http://instagram.com/051.753.6545</t>
+        </is>
+      </c>
+      <c r="I300" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J300" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K300" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L300" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M300" t="inlineStr"/>
+      <c r="N300" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O300" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P300" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q300" t="n">
+        <v>6</v>
+      </c>
+      <c r="R300" t="n">
+        <v>16</v>
+      </c>
+      <c r="S300" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T300" t="inlineStr">
+        <is>
+          <t>1408012420</t>
+        </is>
+      </c>
+      <c r="U300" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1408012420</t>
+        </is>
+      </c>
+      <c r="V300" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>미용실</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>미화</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>wishia@naver.com</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr"/>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>051-752-0825</t>
+        </is>
+      </c>
+      <c r="F301" t="inlineStr"/>
+      <c r="G301" t="inlineStr">
+        <is>
+          <t>부산광역시 수영구 수영로725번길 10</t>
+        </is>
+      </c>
+      <c r="H301" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I301" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J301" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K301" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L301" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M301" t="inlineStr"/>
+      <c r="N301" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O301" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P301" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q301" t="n">
+        <v>0</v>
+      </c>
+      <c r="R301" t="n">
+        <v>2</v>
+      </c>
+      <c r="S301" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T301" t="inlineStr">
+        <is>
+          <t>37981362</t>
+        </is>
+      </c>
+      <c r="U301" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/37981362</t>
+        </is>
+      </c>
+      <c r="V301" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>미용실</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>노트리헤어</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>jeh242@naver.com</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr"/>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>0507-1300-3269</t>
+        </is>
+      </c>
+      <c r="F302" t="inlineStr"/>
+      <c r="G302" t="inlineStr">
+        <is>
+          <t>부산광역시 수영구 수영로702번길 18 3층</t>
+        </is>
+      </c>
+      <c r="H302" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/noteree_official</t>
+        </is>
+      </c>
+      <c r="I302" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J302" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K302" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L302" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M302" t="inlineStr"/>
+      <c r="N302" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O302" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P302" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q302" t="n">
+        <v>0</v>
+      </c>
+      <c r="R302" t="n">
+        <v>20</v>
+      </c>
+      <c r="S302" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T302" t="inlineStr">
+        <is>
+          <t>2039732338</t>
+        </is>
+      </c>
+      <c r="U302" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2039732338</t>
+        </is>
+      </c>
+      <c r="V302" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>미용실</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>픽시크헤어스튜디오</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>maru1707@naver.com</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr"/>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>0507-1465-1699</t>
+        </is>
+      </c>
+      <c r="F303" t="inlineStr"/>
+      <c r="G303" t="inlineStr">
+        <is>
+          <t>부산광역시 수영구 장대골로 8-18 1층</t>
+        </is>
+      </c>
+      <c r="H303" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/fichic_hairstudio/profilecard/?igsh=MXI1dW9pOXVrcWZ4dw==</t>
+        </is>
+      </c>
+      <c r="I303" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J303" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K303" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L303" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M303" t="inlineStr"/>
+      <c r="N303" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O303" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P303" t="n">
+        <v>67</v>
+      </c>
+      <c r="Q303" t="n">
+        <v>8</v>
+      </c>
+      <c r="R303" t="n">
+        <v>75</v>
+      </c>
+      <c r="S303" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T303" t="inlineStr">
+        <is>
+          <t>2098815181</t>
+        </is>
+      </c>
+      <c r="U303" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2098815181</t>
+        </is>
+      </c>
+      <c r="V303" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>미용실</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>송하린헤어본점</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr"/>
+      <c r="D304" t="inlineStr"/>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>0507-1417-1293</t>
+        </is>
+      </c>
+      <c r="F304" t="inlineStr"/>
+      <c r="G304" t="inlineStr">
+        <is>
+          <t>부산광역시 수영구 수영로679번길 22 송하린헤어</t>
+        </is>
+      </c>
+      <c r="H304" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/1248song</t>
+        </is>
+      </c>
+      <c r="I304" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J304" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K304" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L304" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M304" t="inlineStr"/>
+      <c r="N304" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O304" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P304" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q304" t="n">
+        <v>1</v>
+      </c>
+      <c r="R304" t="n">
+        <v>8</v>
+      </c>
+      <c r="S304" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T304" t="inlineStr">
+        <is>
+          <t>1513095149</t>
+        </is>
+      </c>
+      <c r="U304" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1513095149</t>
+        </is>
+      </c>
+      <c r="V304" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>미용실</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>차영주헤어리더</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr"/>
+      <c r="D305" t="inlineStr"/>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>0507-1313-3565</t>
+        </is>
+      </c>
+      <c r="F305" t="inlineStr"/>
+      <c r="G305" t="inlineStr">
+        <is>
+          <t>부산광역시 수영구 망미배산로36번길 67 1층</t>
+        </is>
+      </c>
+      <c r="H305" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I305" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J305" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K305" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L305" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M305" t="inlineStr"/>
+      <c r="N305" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O305" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P305" t="n">
+        <v>22</v>
+      </c>
+      <c r="Q305" t="n">
+        <v>0</v>
+      </c>
+      <c r="R305" t="n">
+        <v>22</v>
+      </c>
+      <c r="S305" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T305" t="inlineStr">
+        <is>
+          <t>1229922566</t>
+        </is>
+      </c>
+      <c r="U305" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1229922566</t>
+        </is>
+      </c>
+      <c r="V305" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>미용실</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>헤어라인</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr"/>
+      <c r="D306" t="inlineStr"/>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>051-758-6910</t>
+        </is>
+      </c>
+      <c r="F306" t="inlineStr"/>
+      <c r="G306" t="inlineStr">
+        <is>
+          <t>부산광역시 수영구 수미로26번길 71</t>
+        </is>
+      </c>
+      <c r="H306" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I306" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J306" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K306" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L306" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M306" t="inlineStr"/>
+      <c r="N306" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O306" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P306" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q306" t="n">
+        <v>0</v>
+      </c>
+      <c r="R306" t="n">
+        <v>12</v>
+      </c>
+      <c r="S306" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T306" t="inlineStr">
+        <is>
+          <t>37982068</t>
+        </is>
+      </c>
+      <c r="U306" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/37982068</t>
+        </is>
+      </c>
+      <c r="V306" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>미용실</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>김남숙헤어샬롱</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr"/>
+      <c r="D307" t="inlineStr"/>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>051-627-1243</t>
+        </is>
+      </c>
+      <c r="F307" t="inlineStr"/>
+      <c r="G307" t="inlineStr">
+        <is>
+          <t>부산광역시 수영구 남천동로24번길 19</t>
+        </is>
+      </c>
+      <c r="H307" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I307" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J307" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K307" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L307" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M307" t="inlineStr"/>
+      <c r="N307" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O307" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P307" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q307" t="n">
+        <v>0</v>
+      </c>
+      <c r="R307" t="n">
+        <v>3</v>
+      </c>
+      <c r="S307" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T307" t="inlineStr">
+        <is>
+          <t>17073038</t>
+        </is>
+      </c>
+      <c r="U307" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/17073038</t>
+        </is>
+      </c>
+      <c r="V307" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>미용실</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>콘크리트헤어 수영점</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>concretehair@naver.com</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr"/>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>0507-1380-1134</t>
+        </is>
+      </c>
+      <c r="F308" t="inlineStr"/>
+      <c r="G308" t="inlineStr">
+        <is>
+          <t>부산광역시 수영구 수영로 639 2층 콘크리트헤어</t>
+        </is>
+      </c>
+      <c r="H308" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/concretehair</t>
+        </is>
+      </c>
+      <c r="I308" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J308" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K308" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L308" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M308" t="inlineStr"/>
+      <c r="N308" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O308" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P308" t="n">
+        <v>4466</v>
+      </c>
+      <c r="Q308" t="n">
+        <v>439</v>
+      </c>
+      <c r="R308" t="n">
+        <v>4905</v>
+      </c>
+      <c r="S308" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T308" t="inlineStr">
+        <is>
+          <t>1429406727</t>
+        </is>
+      </c>
+      <c r="U308" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1429406727</t>
+        </is>
+      </c>
+      <c r="V308" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>두피,탈모관리</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>나와모랩 부산수영구1호점</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>nawamolab@naver.com</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr"/>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>0507-1377-7665</t>
+        </is>
+      </c>
+      <c r="F309" t="inlineStr"/>
+      <c r="G309" t="inlineStr">
+        <is>
+          <t>부산광역시 수영구 수영로741번길 12 105호</t>
+        </is>
+      </c>
+      <c r="H309" t="inlineStr">
+        <is>
+          <t>https://litt.ly/nawamolab</t>
+        </is>
+      </c>
+      <c r="I309" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J309" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K309" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L309" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M309" t="inlineStr"/>
+      <c r="N309" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O309" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P309" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q309" t="n">
+        <v>0</v>
+      </c>
+      <c r="R309" t="n">
+        <v>0</v>
+      </c>
+      <c r="S309" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T309" t="inlineStr">
+        <is>
+          <t>2020236542</t>
+        </is>
+      </c>
+      <c r="U309" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2020236542</t>
+        </is>
+      </c>
+      <c r="V309" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>머리염색</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>구피샵 부산민락점</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr"/>
+      <c r="D310" t="inlineStr"/>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>051-758-1232</t>
+        </is>
+      </c>
+      <c r="F310" t="inlineStr"/>
+      <c r="G310" t="inlineStr">
+        <is>
+          <t>부산광역시 수영구 무학로63번길 142 402동 1층 102호</t>
+        </is>
+      </c>
+      <c r="H310" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I310" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J310" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K310" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L310" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M310" t="inlineStr"/>
+      <c r="N310" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O310" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P310" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q310" t="n">
+        <v>4</v>
+      </c>
+      <c r="R310" t="n">
+        <v>12</v>
+      </c>
+      <c r="S310" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T310" t="inlineStr">
+        <is>
+          <t>2053528475</t>
+        </is>
+      </c>
+      <c r="U310" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2053528475</t>
+        </is>
+      </c>
+      <c r="V310" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>미용</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>해변살롱</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr"/>
+      <c r="D311" t="inlineStr"/>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>051-913-1578</t>
+        </is>
+      </c>
+      <c r="F311" t="inlineStr"/>
+      <c r="G311" t="inlineStr">
+        <is>
+          <t>부산광역시 수영구 수영로388번길 46 2층</t>
+        </is>
+      </c>
+      <c r="H311" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/_marrie_157</t>
+        </is>
+      </c>
+      <c r="I311" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J311" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K311" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L311" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M311" t="inlineStr"/>
+      <c r="N311" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O311" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P311" t="n">
+        <v>88</v>
+      </c>
+      <c r="Q311" t="n">
+        <v>1</v>
+      </c>
+      <c r="R311" t="n">
+        <v>89</v>
+      </c>
+      <c r="S311" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T311" t="inlineStr">
+        <is>
+          <t>1855340486</t>
+        </is>
+      </c>
+      <c r="U311" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1855340486</t>
+        </is>
+      </c>
+      <c r="V311" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>미용</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>샵132</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr"/>
+      <c r="D312" t="inlineStr"/>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>070-3333-3535</t>
+        </is>
+      </c>
+      <c r="F312" t="inlineStr"/>
+      <c r="G312" t="inlineStr">
+        <is>
+          <t>부산광역시 수영구 황령대로473번길 15 1층 132호</t>
+        </is>
+      </c>
+      <c r="H312" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I312" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J312" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K312" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L312" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M312" t="inlineStr"/>
+      <c r="N312" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O312" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P312" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q312" t="n">
+        <v>0</v>
+      </c>
+      <c r="R312" t="n">
+        <v>3</v>
+      </c>
+      <c r="S312" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T312" t="inlineStr">
+        <is>
+          <t>1803491672</t>
+        </is>
+      </c>
+      <c r="U312" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1803491672</t>
+        </is>
+      </c>
+      <c r="V312" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>반려동물미용</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>민츄츄</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr"/>
+      <c r="D313" t="inlineStr"/>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>0507-1327-2177</t>
+        </is>
+      </c>
+      <c r="F313" t="inlineStr"/>
+      <c r="G313" t="inlineStr">
+        <is>
+          <t>부산광역시 수영구 민락본동로11번길 21 민츄츄 애견미용실</t>
+        </is>
+      </c>
+      <c r="H313" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/</t>
+        </is>
+      </c>
+      <c r="I313" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="J313" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K313" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L313" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M313" t="inlineStr"/>
+      <c r="N313" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O313" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P313" t="n">
+        <v>93</v>
+      </c>
+      <c r="Q313" t="n">
+        <v>39</v>
+      </c>
+      <c r="R313" t="n">
+        <v>132</v>
+      </c>
+      <c r="S313" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T313" t="inlineStr">
+        <is>
+          <t>1318955783</t>
+        </is>
+      </c>
+      <c r="U313" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1318955783</t>
+        </is>
+      </c>
+      <c r="V313" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>반려동물미용</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>몽실몽실</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr"/>
+      <c r="D314" t="inlineStr"/>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>0507-1358-0740</t>
+        </is>
+      </c>
+      <c r="F314" t="inlineStr"/>
+      <c r="G314" t="inlineStr">
+        <is>
+          <t>부산광역시 수영구 연수로275번길 34 배산정 1층 102호</t>
+        </is>
+      </c>
+      <c r="H314" t="inlineStr">
+        <is>
+          <t>http://www.instagram.com/mong.sil123</t>
+        </is>
+      </c>
+      <c r="I314" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J314" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K314" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L314" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M314" t="inlineStr"/>
+      <c r="N314" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O314" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P314" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q314" t="n">
+        <v>3</v>
+      </c>
+      <c r="R314" t="n">
+        <v>19</v>
+      </c>
+      <c r="S314" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T314" t="inlineStr">
+        <is>
+          <t>1077781280</t>
+        </is>
+      </c>
+      <c r="U314" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1077781280</t>
+        </is>
+      </c>
+      <c r="V314" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>반려동물미용</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>아띠아몽</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr"/>
+      <c r="D315" t="inlineStr"/>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>0507-1362-9183</t>
+        </is>
+      </c>
+      <c r="F315" t="inlineStr"/>
+      <c r="G315" t="inlineStr">
+        <is>
+          <t>부산광역시 수영구 남천바다로10번길 16 1층 102호</t>
+        </is>
+      </c>
+      <c r="H315" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I315" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J315" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K315" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L315" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M315" t="inlineStr"/>
+      <c r="N315" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O315" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P315" t="n">
+        <v>20</v>
+      </c>
+      <c r="Q315" t="n">
+        <v>3</v>
+      </c>
+      <c r="R315" t="n">
+        <v>23</v>
+      </c>
+      <c r="S315" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T315" t="inlineStr">
+        <is>
+          <t>1439063115</t>
+        </is>
+      </c>
+      <c r="U315" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1439063115</t>
+        </is>
+      </c>
+      <c r="V315" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>반려동물미용</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>동이몽이</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>congzi3388@naver.com</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr"/>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>0507-1496-2520</t>
+        </is>
+      </c>
+      <c r="F316" t="inlineStr"/>
+      <c r="G316" t="inlineStr">
+        <is>
+          <t>부산광역시 수영구 광서로 29 1층</t>
+        </is>
+      </c>
+      <c r="H316" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/dong2mong2_?igsh=azNzbjk2MHIyajc5&amp;utm_source=qr</t>
+        </is>
+      </c>
+      <c r="I316" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J316" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K316" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L316" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M316" t="inlineStr"/>
+      <c r="N316" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="O316" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P316" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q316" t="n">
+        <v>6</v>
+      </c>
+      <c r="R316" t="n">
+        <v>36</v>
+      </c>
+      <c r="S316" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T316" t="inlineStr">
+        <is>
+          <t>1727573089</t>
+        </is>
+      </c>
+      <c r="U316" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1727573089</t>
+        </is>
+      </c>
+      <c r="V316" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>반려동물미용</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>댕댕몽띠끄</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>dd_mongtique@naver.com</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr"/>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>0507-1366-8269</t>
+        </is>
+      </c>
+      <c r="F317" t="inlineStr"/>
+      <c r="G317" t="inlineStr">
+        <is>
+          <t>부산광역시 수영구 과정로 33-1 1층 1층일부</t>
+        </is>
+      </c>
+      <c r="H317" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/dd_mongtique</t>
+        </is>
+      </c>
+      <c r="I317" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J317" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K317" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L317" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M317" t="inlineStr"/>
+      <c r="N317" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O317" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P317" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q317" t="n">
+        <v>27</v>
+      </c>
+      <c r="R317" t="n">
+        <v>41</v>
+      </c>
+      <c r="S317" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T317" t="inlineStr">
+        <is>
+          <t>1765807629</t>
+        </is>
+      </c>
+      <c r="U317" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1765807629</t>
+        </is>
+      </c>
+      <c r="V317" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>반려동물미용</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>개팡&amp;스파샤봉</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>mare2674@naver.com</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr"/>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>0507-1368-5339</t>
+        </is>
+      </c>
+      <c r="F318" t="inlineStr"/>
+      <c r="G318" t="inlineStr">
+        <is>
+          <t>부산광역시 수영구 광남로 149 대권네오텔 1층 개팡&amp;스파샤봉</t>
+        </is>
+      </c>
+      <c r="H318" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/mare2674</t>
+        </is>
+      </c>
+      <c r="I318" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J318" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K318" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L318" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M318" t="inlineStr"/>
+      <c r="N318" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O318" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P318" t="n">
+        <v>341</v>
+      </c>
+      <c r="Q318" t="n">
+        <v>298</v>
+      </c>
+      <c r="R318" t="n">
+        <v>639</v>
+      </c>
+      <c r="S318" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T318" t="inlineStr">
+        <is>
+          <t>1439994884</t>
+        </is>
+      </c>
+      <c r="U318" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1439994884</t>
+        </is>
+      </c>
+      <c r="V318" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>이용원</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>코브바버샵</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>kim900_@naver.com</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr"/>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>0507-1447-7826</t>
+        </is>
+      </c>
+      <c r="F319" t="inlineStr"/>
+      <c r="G319" t="inlineStr">
+        <is>
+          <t>부산광역시 수영구 민락수변로17번길 36 1층 133호</t>
+        </is>
+      </c>
+      <c r="H319" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/cove.barbershop/</t>
+        </is>
+      </c>
+      <c r="I319" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J319" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K319" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L319" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M319" t="inlineStr"/>
+      <c r="N319" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O319" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P319" t="n">
+        <v>174</v>
+      </c>
+      <c r="Q319" t="n">
+        <v>1</v>
+      </c>
+      <c r="R319" t="n">
+        <v>175</v>
+      </c>
+      <c r="S319" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T319" t="inlineStr">
+        <is>
+          <t>2035192863</t>
+        </is>
+      </c>
+      <c r="U319" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2035192863</t>
+        </is>
+      </c>
+      <c r="V319" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>이용원</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>새민락이용원</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>nunnu18@naver.com</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr"/>
+      <c r="E320" t="inlineStr"/>
+      <c r="F320" t="inlineStr"/>
+      <c r="G320" t="inlineStr">
+        <is>
+          <t>부산광역시 수영구 광남로258번길 23</t>
+        </is>
+      </c>
+      <c r="H320" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I320" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J320" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K320" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L320" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M320" t="inlineStr"/>
+      <c r="N320" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O320" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P320" t="n">
+        <v>35</v>
+      </c>
+      <c r="Q320" t="n">
+        <v>0</v>
+      </c>
+      <c r="R320" t="n">
+        <v>35</v>
+      </c>
+      <c r="S320" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T320" t="inlineStr">
+        <is>
+          <t>17061619</t>
+        </is>
+      </c>
+      <c r="U320" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/17061619</t>
+        </is>
+      </c>
+      <c r="V320" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>이용원</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>서던브로스바버샵</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>yaganin@naver.com</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr"/>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>0507-1349-7545</t>
+        </is>
+      </c>
+      <c r="F321" t="inlineStr"/>
+      <c r="G321" t="inlineStr">
+        <is>
+          <t>부산광역시 수영구 광안로16번길 53 1층 101호</t>
+        </is>
+      </c>
+      <c r="H321" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/yaganin</t>
+        </is>
+      </c>
+      <c r="I321" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J321" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K321" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L321" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M321" t="inlineStr"/>
+      <c r="N321" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O321" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P321" t="n">
+        <v>39</v>
+      </c>
+      <c r="Q321" t="n">
+        <v>94</v>
+      </c>
+      <c r="R321" t="n">
+        <v>133</v>
+      </c>
+      <c r="S321" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T321" t="inlineStr">
+        <is>
+          <t>1792037272</t>
+        </is>
+      </c>
+      <c r="U321" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1792037272</t>
+        </is>
+      </c>
+      <c r="V321" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>이용원</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>태창이용원</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>uldesign17@naver.com</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr"/>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>051-751-3587</t>
+        </is>
+      </c>
+      <c r="F322" t="inlineStr"/>
+      <c r="G322" t="inlineStr">
+        <is>
+          <t>부산광역시 수영구 구락로 7</t>
+        </is>
+      </c>
+      <c r="H322" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I322" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J322" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K322" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L322" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M322" t="inlineStr"/>
+      <c r="N322" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O322" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P322" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q322" t="n">
+        <v>0</v>
+      </c>
+      <c r="R322" t="n">
+        <v>0</v>
+      </c>
+      <c r="S322" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T322" t="inlineStr">
+        <is>
+          <t>17058867</t>
+        </is>
+      </c>
+      <c r="U322" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/17058867</t>
+        </is>
+      </c>
+      <c r="V322" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>이용원</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>멋이용원</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>a00031@naver.com</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr"/>
+      <c r="E323" t="inlineStr"/>
+      <c r="F323" t="inlineStr"/>
+      <c r="G323" t="inlineStr">
+        <is>
+          <t>부산광역시 수영구 망미로8번길 50</t>
+        </is>
+      </c>
+      <c r="H323" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I323" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J323" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K323" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L323" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M323" t="inlineStr"/>
+      <c r="N323" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O323" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P323" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q323" t="n">
+        <v>0</v>
+      </c>
+      <c r="R323" t="n">
+        <v>0</v>
+      </c>
+      <c r="S323" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T323" t="inlineStr">
+        <is>
+          <t>1266747351</t>
+        </is>
+      </c>
+      <c r="U323" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1266747351</t>
+        </is>
+      </c>
+      <c r="V323" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>이용원</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>브런스윅바버샵</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr"/>
+      <c r="D324" t="inlineStr"/>
+      <c r="E324" t="inlineStr">
+        <is>
+          <t>0507-1357-8138</t>
+        </is>
+      </c>
+      <c r="F324" t="inlineStr"/>
+      <c r="G324" t="inlineStr">
+        <is>
+          <t>부산광역시 수영구 광안로35번길 11 1층 브런스윅 바버샵</t>
+        </is>
+      </c>
+      <c r="H324" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/brunswick_barbershop</t>
+        </is>
+      </c>
+      <c r="I324" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J324" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K324" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L324" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M324" t="inlineStr"/>
+      <c r="N324" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O324" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P324" t="n">
+        <v>480</v>
+      </c>
+      <c r="Q324" t="n">
+        <v>11</v>
+      </c>
+      <c r="R324" t="n">
+        <v>491</v>
+      </c>
+      <c r="S324" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T324" t="inlineStr">
+        <is>
+          <t>1965591482</t>
+        </is>
+      </c>
+      <c r="U324" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1965591482</t>
+        </is>
+      </c>
+      <c r="V324" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>이용원</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>좋은인상이용원</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr"/>
+      <c r="D325" t="inlineStr"/>
+      <c r="E325" t="inlineStr"/>
+      <c r="F325" t="inlineStr"/>
+      <c r="G325" t="inlineStr">
+        <is>
+          <t>부산광역시 수영구 좌수영로83번길 28</t>
+        </is>
+      </c>
+      <c r="H325" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I325" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J325" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K325" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L325" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M325" t="inlineStr"/>
+      <c r="N325" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O325" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P325" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q325" t="n">
+        <v>0</v>
+      </c>
+      <c r="R325" t="n">
+        <v>2</v>
+      </c>
+      <c r="S325" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T325" t="inlineStr">
+        <is>
+          <t>1138097691</t>
+        </is>
+      </c>
+      <c r="U325" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1138097691</t>
+        </is>
+      </c>
+      <c r="V325" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>이용원</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>빅가이바버샵</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>freehoo2@naver.com</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr"/>
+      <c r="E326" t="inlineStr">
+        <is>
+          <t>0507-1321-6575</t>
+        </is>
+      </c>
+      <c r="F326" t="inlineStr"/>
+      <c r="G326" t="inlineStr">
+        <is>
+          <t>부산광역시 수영구 망미번영로52번길 39 1층 골목 첫번째 상가</t>
+        </is>
+      </c>
+      <c r="H326" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/freehoo2</t>
+        </is>
+      </c>
+      <c r="I326" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J326" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K326" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L326" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M326" t="inlineStr"/>
+      <c r="N326" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O326" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P326" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q326" t="n">
+        <v>66</v>
+      </c>
+      <c r="R326" t="n">
+        <v>72</v>
+      </c>
+      <c r="S326" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T326" t="inlineStr">
+        <is>
+          <t>1033478003</t>
+        </is>
+      </c>
+      <c r="U326" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1033478003</t>
+        </is>
+      </c>
+      <c r="V326" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>이용원</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>드라이빌 바버샵</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>dryville@naver.com</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr"/>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>0507-1352-9061</t>
+        </is>
+      </c>
+      <c r="F327" t="inlineStr"/>
+      <c r="G327" t="inlineStr">
+        <is>
+          <t>부산광역시 수영구 수영로394번길 23 1층</t>
+        </is>
+      </c>
+      <c r="H327" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/dryville</t>
+        </is>
+      </c>
+      <c r="I327" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J327" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K327" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L327" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M327" t="inlineStr"/>
+      <c r="N327" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O327" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P327" t="n">
+        <v>166</v>
+      </c>
+      <c r="Q327" t="n">
+        <v>11</v>
+      </c>
+      <c r="R327" t="n">
+        <v>177</v>
+      </c>
+      <c r="S327" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T327" t="inlineStr">
+        <is>
+          <t>2064471377</t>
+        </is>
+      </c>
+      <c r="U327" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2064471377</t>
+        </is>
+      </c>
+      <c r="V327" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>이용원</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>나모 바버샵</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr"/>
+      <c r="D328" t="inlineStr"/>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>0507-1311-7302</t>
+        </is>
+      </c>
+      <c r="F328" t="inlineStr"/>
+      <c r="G328" t="inlineStr">
+        <is>
+          <t>부산광역시 수영구 남천바다로22번길 28 1층</t>
+        </is>
+      </c>
+      <c r="H328" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/namobarbershop/</t>
+        </is>
+      </c>
+      <c r="I328" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J328" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K328" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L328" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M328" t="inlineStr"/>
+      <c r="N328" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O328" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P328" t="n">
+        <v>1576</v>
+      </c>
+      <c r="Q328" t="n">
+        <v>343</v>
+      </c>
+      <c r="R328" t="n">
+        <v>1919</v>
+      </c>
+      <c r="S328" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T328" t="inlineStr">
+        <is>
+          <t>37672836</t>
+        </is>
+      </c>
+      <c r="U328" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/37672836</t>
+        </is>
+      </c>
+      <c r="V328" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>이용원</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>대성이용원</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr"/>
+      <c r="D329" t="inlineStr"/>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>051-753-4797</t>
+        </is>
+      </c>
+      <c r="F329" t="inlineStr"/>
+      <c r="G329" t="inlineStr">
+        <is>
+          <t>부산광역시 수영구 수미로50번길 37-1</t>
+        </is>
+      </c>
+      <c r="H329" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I329" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J329" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K329" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L329" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M329" t="inlineStr"/>
+      <c r="N329" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O329" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P329" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q329" t="n">
+        <v>0</v>
+      </c>
+      <c r="R329" t="n">
+        <v>0</v>
+      </c>
+      <c r="S329" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T329" t="inlineStr">
+        <is>
+          <t>37981888</t>
+        </is>
+      </c>
+      <c r="U329" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/37981888</t>
+        </is>
+      </c>
+      <c r="V329" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>이용원</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>코이프바버샵</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>museopbarber@naver.com</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr"/>
+      <c r="E330" t="inlineStr"/>
+      <c r="F330" t="inlineStr"/>
+      <c r="G330" t="inlineStr">
+        <is>
+          <t>부산광역시 수영구 수영로652번길 46 1층</t>
+        </is>
+      </c>
+      <c r="H330" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/coifbarbershop/</t>
+        </is>
+      </c>
+      <c r="I330" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J330" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K330" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L330" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M330" t="inlineStr"/>
+      <c r="N330" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O330" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P330" t="n">
+        <v>469</v>
+      </c>
+      <c r="Q330" t="n">
+        <v>36</v>
+      </c>
+      <c r="R330" t="n">
+        <v>505</v>
+      </c>
+      <c r="S330" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T330" t="inlineStr">
+        <is>
+          <t>1824221711</t>
+        </is>
+      </c>
+      <c r="U330" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1824221711</t>
+        </is>
+      </c>
+      <c r="V330" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>이용원</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>대진이용원</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>daejinuniv@naver.com</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr"/>
+      <c r="E331" t="inlineStr"/>
+      <c r="F331" t="inlineStr"/>
+      <c r="G331" t="inlineStr">
+        <is>
+          <t>부산광역시 수영구 민락로27번길 26</t>
+        </is>
+      </c>
+      <c r="H331" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I331" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J331" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K331" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L331" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M331" t="inlineStr"/>
+      <c r="N331" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O331" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P331" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q331" t="n">
+        <v>1</v>
+      </c>
+      <c r="R331" t="n">
+        <v>1</v>
+      </c>
+      <c r="S331" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T331" t="inlineStr">
+        <is>
+          <t>17062837</t>
+        </is>
+      </c>
+      <c r="U331" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/17062837</t>
+        </is>
+      </c>
+      <c r="V331" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>인테리어디자인</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>페니디자인</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>mond0120@naver.com</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr"/>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>0507-1488-1499</t>
+        </is>
+      </c>
+      <c r="F332" t="inlineStr"/>
+      <c r="G332" t="inlineStr">
+        <is>
+          <t>부산광역시 수영구 광안로61번길 12 페니디자인</t>
+        </is>
+      </c>
+      <c r="H332" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I332" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J332" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K332" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L332" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M332" t="inlineStr"/>
+      <c r="N332" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O332" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P332" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q332" t="n">
+        <v>3</v>
+      </c>
+      <c r="R332" t="n">
+        <v>3</v>
+      </c>
+      <c r="S332" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T332" t="inlineStr">
+        <is>
           <t>31786317</t>
         </is>
       </c>
-      <c r="U259" t="inlineStr">
+      <c r="U332" t="inlineStr">
         <is>
           <t>https://m.place.naver.com/place/31786317</t>
         </is>
       </c>
-      <c r="V259" t="inlineStr">
+      <c r="V332" t="inlineStr">
         <is>
           <t>2026-04-17</t>
         </is>
